--- a/student_program_level_output.xlsx
+++ b/student_program_level_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,38 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F494"/>
+  <dimension ref="A1:G494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>acad_plan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tuition</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>scholarship</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>program</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net_tuition</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>intl</t>
         </is>
       </c>
     </row>
@@ -483,6 +476,9 @@
       <c r="F2" t="n">
         <v>39786.4</v>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,6 +503,9 @@
       <c r="F3" t="n">
         <v>93490</v>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -531,6 +530,9 @@
       <c r="F4" t="n">
         <v>16266</v>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -555,6 +557,9 @@
       <c r="F5" t="n">
         <v>58399</v>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -579,6 +584,9 @@
       <c r="F6" t="n">
         <v>119800</v>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -603,6 +611,9 @@
       <c r="F7" t="n">
         <v>34287</v>
       </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -627,6 +638,9 @@
       <c r="F8" t="n">
         <v>24399</v>
       </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -651,6 +665,9 @@
       <c r="F9" t="n">
         <v>71648</v>
       </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -675,6 +692,9 @@
       <c r="F10" t="n">
         <v>71719</v>
       </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -699,6 +719,9 @@
       <c r="F11" t="n">
         <v>23610</v>
       </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -723,6 +746,9 @@
       <c r="F12" t="n">
         <v>30800</v>
       </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -747,6 +773,9 @@
       <c r="F13" t="n">
         <v>30531</v>
       </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -771,6 +800,9 @@
       <c r="F14" t="n">
         <v>26800</v>
       </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -795,6 +827,9 @@
       <c r="F15" t="n">
         <v>16254</v>
       </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -819,6 +854,9 @@
       <c r="F16" t="n">
         <v>74100</v>
       </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -843,6 +881,9 @@
       <c r="F17" t="n">
         <v>66210</v>
       </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -867,6 +908,9 @@
       <c r="F18" t="n">
         <v>76703</v>
       </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -891,6 +935,9 @@
       <c r="F19" t="n">
         <v>63298</v>
       </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -915,6 +962,9 @@
       <c r="F20" t="n">
         <v>52582</v>
       </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -939,6 +989,9 @@
       <c r="F21" t="n">
         <v>82404</v>
       </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -963,6 +1016,9 @@
       <c r="F22" t="n">
         <v>36532</v>
       </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -987,6 +1043,9 @@
       <c r="F23" t="n">
         <v>44600</v>
       </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1011,6 +1070,9 @@
       <c r="F24" t="n">
         <v>18812</v>
       </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1035,6 +1097,9 @@
       <c r="F25" t="n">
         <v>77600</v>
       </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1059,6 +1124,9 @@
       <c r="F26" t="n">
         <v>46800</v>
       </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1083,6 +1151,9 @@
       <c r="F27" t="n">
         <v>29280</v>
       </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1107,6 +1178,9 @@
       <c r="F28" t="n">
         <v>9488</v>
       </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1131,6 +1205,9 @@
       <c r="F29" t="n">
         <v>10844</v>
       </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1155,6 +1232,9 @@
       <c r="F30" t="n">
         <v>50600</v>
       </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1179,6 +1259,9 @@
       <c r="F31" t="n">
         <v>31800</v>
       </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1203,6 +1286,9 @@
       <c r="F32" t="n">
         <v>68529</v>
       </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1227,6 +1313,9 @@
       <c r="F33" t="n">
         <v>71945</v>
       </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1251,6 +1340,9 @@
       <c r="F34" t="n">
         <v>25000</v>
       </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1275,6 +1367,9 @@
       <c r="F35" t="n">
         <v>44650</v>
       </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1299,6 +1394,9 @@
       <c r="F36" t="n">
         <v>52616</v>
       </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1323,6 +1421,9 @@
       <c r="F37" t="n">
         <v>41800</v>
       </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1347,6 +1448,9 @@
       <c r="F38" t="n">
         <v>77470</v>
       </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1371,6 +1475,9 @@
       <c r="F39" t="n">
         <v>35166</v>
       </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1395,6 +1502,9 @@
       <c r="F40" t="n">
         <v>68300</v>
       </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1419,6 +1529,9 @@
       <c r="F41" t="n">
         <v>49552</v>
       </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1443,6 +1556,9 @@
       <c r="F42" t="n">
         <v>40600</v>
       </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1467,6 +1583,9 @@
       <c r="F43" t="n">
         <v>50600</v>
       </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1491,6 +1610,9 @@
       <c r="F44" t="n">
         <v>64600</v>
       </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1515,6 +1637,9 @@
       <c r="F45" t="n">
         <v>31778</v>
       </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1539,6 +1664,9 @@
       <c r="F46" t="n">
         <v>11610</v>
       </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1563,6 +1691,9 @@
       <c r="F47" t="n">
         <v>23800</v>
       </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1587,6 +1718,9 @@
       <c r="F48" t="n">
         <v>58600</v>
       </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1611,6 +1745,9 @@
       <c r="F49" t="n">
         <v>22400</v>
       </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1635,6 +1772,9 @@
       <c r="F50" t="n">
         <v>58600</v>
       </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1659,6 +1799,9 @@
       <c r="F51" t="n">
         <v>23232</v>
       </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1683,6 +1826,9 @@
       <c r="F52" t="n">
         <v>58424</v>
       </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1707,6 +1853,9 @@
       <c r="F53" t="n">
         <v>21900</v>
       </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1731,6 +1880,9 @@
       <c r="F54" t="n">
         <v>44300</v>
       </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1755,6 +1907,9 @@
       <c r="F55" t="n">
         <v>61879</v>
       </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1779,6 +1934,9 @@
       <c r="F56" t="n">
         <v>41800</v>
       </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1803,6 +1961,9 @@
       <c r="F57" t="n">
         <v>18800</v>
       </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1827,6 +1988,9 @@
       <c r="F58" t="n">
         <v>41610</v>
       </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1851,6 +2015,9 @@
       <c r="F59" t="n">
         <v>64600</v>
       </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1875,6 +2042,9 @@
       <c r="F60" t="n">
         <v>43050</v>
       </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1899,6 +2069,9 @@
       <c r="F61" t="n">
         <v>41800</v>
       </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1923,6 +2096,9 @@
       <c r="F62" t="n">
         <v>67456</v>
       </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1947,6 +2123,9 @@
       <c r="F63" t="n">
         <v>53742</v>
       </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1971,6 +2150,9 @@
       <c r="F64" t="n">
         <v>36328</v>
       </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1995,6 +2177,9 @@
       <c r="F65" t="n">
         <v>57780</v>
       </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2019,6 +2204,9 @@
       <c r="F66" t="n">
         <v>44050</v>
       </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2041,7 +2229,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-4529</v>
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2067,6 +2258,9 @@
       <c r="F68" t="n">
         <v>44050</v>
       </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2091,6 +2285,9 @@
       <c r="F69" t="n">
         <v>41800</v>
       </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2115,6 +2312,9 @@
       <c r="F70" t="n">
         <v>21400</v>
       </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2139,6 +2339,9 @@
       <c r="F71" t="n">
         <v>33539</v>
       </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2163,6 +2366,9 @@
       <c r="F72" t="n">
         <v>44050</v>
       </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2187,6 +2393,9 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2211,6 +2420,9 @@
       <c r="F74" t="n">
         <v>44122</v>
       </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2235,6 +2447,9 @@
       <c r="F75" t="n">
         <v>45050</v>
       </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2259,6 +2474,9 @@
       <c r="F76" t="n">
         <v>45050</v>
       </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2283,6 +2501,9 @@
       <c r="F77" t="n">
         <v>65700</v>
       </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2307,6 +2528,9 @@
       <c r="F78" t="n">
         <v>45050</v>
       </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2331,6 +2555,9 @@
       <c r="F79" t="n">
         <v>12164</v>
       </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2355,6 +2582,9 @@
       <c r="F80" t="n">
         <v>45050</v>
       </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2379,6 +2609,9 @@
       <c r="F81" t="n">
         <v>43800</v>
       </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2403,6 +2636,9 @@
       <c r="F82" t="n">
         <v>22839</v>
       </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2427,6 +2663,9 @@
       <c r="F83" t="n">
         <v>54989</v>
       </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2451,6 +2690,9 @@
       <c r="F84" t="n">
         <v>21900</v>
       </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2475,6 +2717,9 @@
       <c r="F85" t="n">
         <v>38933</v>
       </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2499,6 +2744,9 @@
       <c r="F86" t="n">
         <v>9288</v>
       </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2523,6 +2771,9 @@
       <c r="F87" t="n">
         <v>16600</v>
       </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2547,6 +2798,9 @@
       <c r="F88" t="n">
         <v>3483</v>
       </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2571,6 +2825,9 @@
       <c r="F89" t="n">
         <v>40953</v>
       </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2595,6 +2852,9 @@
       <c r="F90" t="n">
         <v>10450</v>
       </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2619,6 +2879,9 @@
       <c r="F91" t="n">
         <v>17416</v>
       </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2643,6 +2906,9 @@
       <c r="F92" t="n">
         <v>21800</v>
       </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2667,6 +2933,9 @@
       <c r="F93" t="n">
         <v>26800</v>
       </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2691,6 +2960,9 @@
       <c r="F94" t="n">
         <v>3483</v>
       </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2715,6 +2987,9 @@
       <c r="F95" t="n">
         <v>21900</v>
       </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2739,6 +3014,9 @@
       <c r="F96" t="n">
         <v>59734</v>
       </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2763,6 +3041,9 @@
       <c r="F97" t="n">
         <v>60600</v>
       </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2787,6 +3068,9 @@
       <c r="F98" t="n">
         <v>10950</v>
       </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2811,6 +3095,9 @@
       <c r="F99" t="n">
         <v>40143</v>
       </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2835,6 +3122,9 @@
       <c r="F100" t="n">
         <v>44800</v>
       </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2859,6 +3149,9 @@
       <c r="F101" t="n">
         <v>20900</v>
       </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2883,6 +3176,9 @@
       <c r="F102" t="n">
         <v>20900</v>
       </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2907,6 +3203,9 @@
       <c r="F103" t="n">
         <v>63060</v>
       </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2931,6 +3230,9 @@
       <c r="F104" t="n">
         <v>24383</v>
       </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2955,6 +3257,9 @@
       <c r="F105" t="n">
         <v>43990</v>
       </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2979,6 +3284,9 @@
       <c r="F106" t="n">
         <v>16800</v>
       </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3003,6 +3311,9 @@
       <c r="F107" t="n">
         <v>46131</v>
       </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3027,6 +3338,9 @@
       <c r="F108" t="n">
         <v>33182</v>
       </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3051,6 +3365,9 @@
       <c r="F109" t="n">
         <v>41494</v>
       </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3075,6 +3392,9 @@
       <c r="F110" t="n">
         <v>49945</v>
       </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3099,6 +3419,9 @@
       <c r="F111" t="n">
         <v>40320</v>
       </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3123,6 +3446,9 @@
       <c r="F112" t="n">
         <v>46050</v>
       </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3147,6 +3473,9 @@
       <c r="F113" t="n">
         <v>29224</v>
       </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3171,6 +3500,9 @@
       <c r="F114" t="n">
         <v>10450</v>
       </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3195,6 +3527,9 @@
       <c r="F115" t="n">
         <v>22800</v>
       </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3219,6 +3554,9 @@
       <c r="F116" t="n">
         <v>15094</v>
       </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3243,6 +3581,9 @@
       <c r="F117" t="n">
         <v>11800</v>
       </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3267,6 +3608,9 @@
       <c r="F118" t="n">
         <v>10450</v>
       </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3291,6 +3635,9 @@
       <c r="F119" t="n">
         <v>10450</v>
       </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3315,6 +3662,9 @@
       <c r="F120" t="n">
         <v>16800</v>
       </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3339,6 +3689,9 @@
       <c r="F121" t="n">
         <v>21800</v>
       </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3363,6 +3716,9 @@
       <c r="F122" t="n">
         <v>10450</v>
       </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3387,6 +3743,9 @@
       <c r="F123" t="n">
         <v>18577</v>
       </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3411,6 +3770,9 @@
       <c r="F124" t="n">
         <v>62700</v>
       </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3435,6 +3797,9 @@
       <c r="F125" t="n">
         <v>56745</v>
       </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3459,6 +3824,9 @@
       <c r="F126" t="n">
         <v>17416</v>
       </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3483,6 +3851,9 @@
       <c r="F127" t="n">
         <v>17416</v>
       </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3507,6 +3878,9 @@
       <c r="F128" t="n">
         <v>21800</v>
       </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3531,6 +3905,9 @@
       <c r="F129" t="n">
         <v>18577</v>
       </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3555,6 +3932,9 @@
       <c r="F130" t="n">
         <v>17416</v>
       </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3579,6 +3959,9 @@
       <c r="F131" t="n">
         <v>54600</v>
       </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3603,6 +3986,9 @@
       <c r="F132" t="n">
         <v>23800</v>
       </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3627,6 +4013,9 @@
       <c r="F133" t="n">
         <v>47050</v>
       </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3651,6 +4040,9 @@
       <c r="F134" t="n">
         <v>45800</v>
       </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3675,6 +4067,9 @@
       <c r="F135" t="n">
         <v>30532</v>
       </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3699,6 +4094,9 @@
       <c r="F136" t="n">
         <v>48600</v>
       </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3723,6 +4121,9 @@
       <c r="F137" t="n">
         <v>41220</v>
       </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3747,6 +4148,9 @@
       <c r="F138" t="n">
         <v>54600</v>
       </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3771,6 +4175,9 @@
       <c r="F139" t="n">
         <v>50855</v>
       </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3795,6 +4202,9 @@
       <c r="F140" t="n">
         <v>47050</v>
       </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3819,6 +4229,9 @@
       <c r="F141" t="n">
         <v>54981</v>
       </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3843,6 +4256,9 @@
       <c r="F142" t="n">
         <v>59770</v>
       </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3867,6 +4283,9 @@
       <c r="F143" t="n">
         <v>32761</v>
       </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3891,6 +4310,9 @@
       <c r="F144" t="n">
         <v>44600</v>
       </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3915,6 +4337,9 @@
       <c r="F145" t="n">
         <v>52374</v>
       </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3939,6 +4364,9 @@
       <c r="F146" t="n">
         <v>16600</v>
       </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3963,6 +4391,9 @@
       <c r="F147" t="n">
         <v>24300</v>
       </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3987,6 +4418,9 @@
       <c r="F148" t="n">
         <v>36328</v>
       </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4011,6 +4445,9 @@
       <c r="F149" t="n">
         <v>20900</v>
       </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4035,6 +4472,9 @@
       <c r="F150" t="n">
         <v>46050</v>
       </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4059,6 +4499,9 @@
       <c r="F151" t="n">
         <v>36600</v>
       </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4083,6 +4526,9 @@
       <c r="F152" t="n">
         <v>47050</v>
       </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -4107,6 +4553,9 @@
       <c r="F153" t="n">
         <v>42300</v>
       </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4131,6 +4580,9 @@
       <c r="F154" t="n">
         <v>24600</v>
       </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4155,6 +4607,9 @@
       <c r="F155" t="n">
         <v>15266</v>
       </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4179,6 +4634,9 @@
       <c r="F156" t="n">
         <v>22900</v>
       </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4203,6 +4661,9 @@
       <c r="F157" t="n">
         <v>60600</v>
       </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4227,6 +4688,9 @@
       <c r="F158" t="n">
         <v>36600</v>
       </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4251,6 +4715,9 @@
       <c r="F159" t="n">
         <v>34600</v>
       </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4275,6 +4742,9 @@
       <c r="F160" t="n">
         <v>48600</v>
       </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4299,6 +4769,9 @@
       <c r="F161" t="n">
         <v>34600</v>
       </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4323,6 +4796,9 @@
       <c r="F162" t="n">
         <v>66600</v>
       </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4347,6 +4823,9 @@
       <c r="F163" t="n">
         <v>46600</v>
       </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4371,6 +4850,9 @@
       <c r="F164" t="n">
         <v>39923</v>
       </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4395,6 +4877,9 @@
       <c r="F165" t="n">
         <v>54690</v>
       </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4419,6 +4904,9 @@
       <c r="F166" t="n">
         <v>36356</v>
       </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4443,6 +4931,9 @@
       <c r="F167" t="n">
         <v>42300</v>
       </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4467,6 +4958,9 @@
       <c r="F168" t="n">
         <v>39895</v>
       </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4491,6 +4985,9 @@
       <c r="F169" t="n">
         <v>36600</v>
       </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4515,6 +5012,9 @@
       <c r="F170" t="n">
         <v>126900</v>
       </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4539,6 +5039,9 @@
       <c r="F171" t="n">
         <v>36356</v>
       </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4563,6 +5066,9 @@
       <c r="F172" t="n">
         <v>36356</v>
       </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4587,6 +5093,9 @@
       <c r="F173" t="n">
         <v>42300</v>
       </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4611,6 +5120,9 @@
       <c r="F174" t="n">
         <v>42300</v>
       </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4635,6 +5147,9 @@
       <c r="F175" t="n">
         <v>35168</v>
       </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4659,6 +5174,9 @@
       <c r="F176" t="n">
         <v>36356</v>
       </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4683,6 +5201,9 @@
       <c r="F177" t="n">
         <v>46300</v>
       </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4707,6 +5228,9 @@
       <c r="F178" t="n">
         <v>115012</v>
       </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4731,6 +5255,9 @@
       <c r="F179" t="n">
         <v>39895</v>
       </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4755,6 +5282,9 @@
       <c r="F180" t="n">
         <v>36356</v>
       </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4779,6 +5309,9 @@
       <c r="F181" t="n">
         <v>47480</v>
       </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4803,6 +5336,9 @@
       <c r="F182" t="n">
         <v>42300</v>
       </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4827,6 +5363,9 @@
       <c r="F183" t="n">
         <v>36356</v>
       </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4851,6 +5390,9 @@
       <c r="F184" t="n">
         <v>56160</v>
       </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4875,6 +5417,9 @@
       <c r="F185" t="n">
         <v>46800</v>
       </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4899,6 +5444,9 @@
       <c r="F186" t="n">
         <v>69852</v>
       </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4923,6 +5471,9 @@
       <c r="F187" t="n">
         <v>40167</v>
       </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4947,6 +5498,9 @@
       <c r="F188" t="n">
         <v>16380</v>
       </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4971,6 +5525,9 @@
       <c r="F189" t="n">
         <v>48050</v>
       </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4995,6 +5552,9 @@
       <c r="F190" t="n">
         <v>32800</v>
       </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -5019,6 +5579,9 @@
       <c r="F191" t="n">
         <v>23400</v>
       </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5043,6 +5606,9 @@
       <c r="F192" t="n">
         <v>39076</v>
       </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -5067,6 +5633,9 @@
       <c r="F193" t="n">
         <v>48600</v>
       </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -5091,6 +5660,9 @@
       <c r="F194" t="n">
         <v>42020</v>
       </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5115,6 +5687,9 @@
       <c r="F195" t="n">
         <v>108000</v>
       </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5139,6 +5714,9 @@
       <c r="F196" t="n">
         <v>36600</v>
       </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5163,6 +5741,9 @@
       <c r="F197" t="n">
         <v>26600</v>
       </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5187,6 +5768,9 @@
       <c r="F198" t="n">
         <v>68600</v>
       </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -5211,6 +5795,9 @@
       <c r="F199" t="n">
         <v>36350</v>
       </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5235,6 +5822,9 @@
       <c r="F200" t="n">
         <v>62600</v>
       </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -5259,6 +5849,9 @@
       <c r="F201" t="n">
         <v>50600</v>
       </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -5283,6 +5876,9 @@
       <c r="F202" t="n">
         <v>24650</v>
       </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5307,6 +5903,9 @@
       <c r="F203" t="n">
         <v>26600</v>
       </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5331,6 +5930,9 @@
       <c r="F204" t="n">
         <v>108000</v>
       </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5355,6 +5957,9 @@
       <c r="F205" t="n">
         <v>56600</v>
       </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5379,6 +5984,9 @@
       <c r="F206" t="n">
         <v>26600</v>
       </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5403,6 +6011,9 @@
       <c r="F207" t="n">
         <v>66600</v>
       </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5427,6 +6038,9 @@
       <c r="F208" t="n">
         <v>19300</v>
       </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5451,6 +6065,9 @@
       <c r="F209" t="n">
         <v>16600</v>
       </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5475,6 +6092,9 @@
       <c r="F210" t="n">
         <v>38432</v>
       </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5499,6 +6119,9 @@
       <c r="F211" t="n">
         <v>38600</v>
       </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5523,6 +6146,9 @@
       <c r="F212" t="n">
         <v>32350</v>
       </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5547,6 +6173,9 @@
       <c r="F213" t="n">
         <v>40865</v>
       </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5571,6 +6200,9 @@
       <c r="F214" t="n">
         <v>56600</v>
       </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -5595,6 +6227,9 @@
       <c r="F215" t="n">
         <v>32432</v>
       </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -5619,6 +6254,9 @@
       <c r="F216" t="n">
         <v>36333</v>
       </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5643,6 +6281,9 @@
       <c r="F217" t="n">
         <v>36600</v>
       </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5667,6 +6308,9 @@
       <c r="F218" t="n">
         <v>58398</v>
       </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5691,6 +6335,9 @@
       <c r="F219" t="n">
         <v>37216</v>
       </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5715,6 +6362,9 @@
       <c r="F220" t="n">
         <v>41220</v>
       </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5739,6 +6389,9 @@
       <c r="F221" t="n">
         <v>45733</v>
       </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5763,6 +6416,9 @@
       <c r="F222" t="n">
         <v>54500</v>
       </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5787,6 +6443,9 @@
       <c r="F223" t="n">
         <v>44050</v>
       </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5811,6 +6470,9 @@
       <c r="F224" t="n">
         <v>33566</v>
       </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5835,6 +6497,9 @@
       <c r="F225" t="n">
         <v>38811</v>
       </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5859,6 +6524,9 @@
       <c r="F226" t="n">
         <v>29280</v>
       </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5877,11 +6545,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F227" t="n">
         <v>23900</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -5907,6 +6578,9 @@
       <c r="F228" t="n">
         <v>46398</v>
       </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5925,11 +6599,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F229" t="n">
         <v>39040</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -5955,6 +6632,9 @@
       <c r="F230" t="n">
         <v>19520</v>
       </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5979,6 +6659,9 @@
       <c r="F231" t="n">
         <v>47800</v>
       </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6003,6 +6686,9 @@
       <c r="F232" t="n">
         <v>15934</v>
       </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6027,6 +6713,9 @@
       <c r="F233" t="n">
         <v>37800</v>
       </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6051,6 +6740,9 @@
       <c r="F234" t="n">
         <v>15936</v>
       </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -6069,11 +6761,14 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F235" t="n">
         <v>23900</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -6093,11 +6788,14 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F236" t="n">
         <v>23900</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -6123,6 +6821,9 @@
       <c r="F237" t="n">
         <v>48800</v>
       </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -6141,11 +6842,14 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F238" t="n">
         <v>23900</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -6171,6 +6875,9 @@
       <c r="F239" t="n">
         <v>42699</v>
       </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -6195,6 +6902,9 @@
       <c r="F240" t="n">
         <v>46398</v>
       </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -6219,6 +6929,9 @@
       <c r="F241" t="n">
         <v>32750</v>
       </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6243,6 +6956,9 @@
       <c r="F242" t="n">
         <v>48600</v>
       </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -6267,6 +6983,9 @@
       <c r="F243" t="n">
         <v>58600</v>
       </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -6291,6 +7010,9 @@
       <c r="F244" t="n">
         <v>45411</v>
       </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -6309,11 +7031,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F245" t="n">
         <v>23900</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -6333,11 +7058,14 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F246" t="n">
         <v>23900</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -6363,6 +7091,9 @@
       <c r="F247" t="n">
         <v>11200</v>
       </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -6387,6 +7118,9 @@
       <c r="F248" t="n">
         <v>28600</v>
       </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6411,6 +7145,9 @@
       <c r="F249" t="n">
         <v>50600</v>
       </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6435,6 +7172,9 @@
       <c r="F250" t="n">
         <v>48600</v>
       </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6459,6 +7199,9 @@
       <c r="F251" t="n">
         <v>48600</v>
       </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6483,6 +7226,9 @@
       <c r="F252" t="n">
         <v>45300</v>
       </c>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -6507,6 +7253,9 @@
       <c r="F253" t="n">
         <v>47289</v>
       </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -6531,6 +7280,9 @@
       <c r="F254" t="n">
         <v>44300</v>
       </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -6555,6 +7307,9 @@
       <c r="F255" t="n">
         <v>68600</v>
       </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -6579,6 +7334,9 @@
       <c r="F256" t="n">
         <v>135900</v>
       </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -6603,6 +7361,9 @@
       <c r="F257" t="n">
         <v>55965</v>
       </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -6627,6 +7388,9 @@
       <c r="F258" t="n">
         <v>68600</v>
       </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -6651,6 +7415,9 @@
       <c r="F259" t="n">
         <v>42600</v>
       </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -6675,6 +7442,9 @@
       <c r="F260" t="n">
         <v>38600</v>
       </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -6699,6 +7469,9 @@
       <c r="F261" t="n">
         <v>31700</v>
       </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -6723,6 +7496,9 @@
       <c r="F262" t="n">
         <v>36833</v>
       </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -6747,6 +7523,9 @@
       <c r="F263" t="n">
         <v>48600</v>
       </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -6771,6 +7550,9 @@
       <c r="F264" t="n">
         <v>48600</v>
       </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -6795,6 +7577,9 @@
       <c r="F265" t="n">
         <v>48600</v>
       </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6819,6 +7604,9 @@
       <c r="F266" t="n">
         <v>69129</v>
       </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6843,6 +7631,9 @@
       <c r="F267" t="n">
         <v>77912</v>
       </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6867,6 +7658,9 @@
       <c r="F268" t="n">
         <v>38938</v>
       </c>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6891,6 +7685,9 @@
       <c r="F269" t="n">
         <v>48800</v>
       </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6915,6 +7712,9 @@
       <c r="F270" t="n">
         <v>43920</v>
       </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6939,6 +7739,9 @@
       <c r="F271" t="n">
         <v>39040</v>
       </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6963,6 +7766,9 @@
       <c r="F272" t="n">
         <v>24400</v>
       </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -6987,6 +7793,9 @@
       <c r="F273" t="n">
         <v>50050</v>
       </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -7011,6 +7820,9 @@
       <c r="F274" t="n">
         <v>48800</v>
       </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -7035,6 +7847,9 @@
       <c r="F275" t="n">
         <v>16266</v>
       </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -7053,11 +7868,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F276" t="n">
         <v>39040</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -7077,11 +7895,14 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F277" t="n">
         <v>39040</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -7107,6 +7928,9 @@
       <c r="F278" t="n">
         <v>24400</v>
       </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -7131,6 +7955,9 @@
       <c r="F279" t="n">
         <v>52932</v>
       </c>
+      <c r="G279" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -7155,6 +7982,9 @@
       <c r="F280" t="n">
         <v>43470</v>
       </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -7179,6 +8009,9 @@
       <c r="F281" t="n">
         <v>50050</v>
       </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -7203,6 +8036,9 @@
       <c r="F282" t="n">
         <v>34744</v>
       </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -7227,6 +8063,9 @@
       <c r="F283" t="n">
         <v>50050</v>
       </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -7251,6 +8090,9 @@
       <c r="F284" t="n">
         <v>24400</v>
       </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -7275,6 +8117,9 @@
       <c r="F285" t="n">
         <v>70600</v>
       </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -7299,6 +8144,9 @@
       <c r="F286" t="n">
         <v>60600</v>
       </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -7323,6 +8171,9 @@
       <c r="F287" t="n">
         <v>41480</v>
       </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -7347,6 +8198,9 @@
       <c r="F288" t="n">
         <v>45300</v>
       </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -7371,6 +8225,9 @@
       <c r="F289" t="n">
         <v>40600</v>
       </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -7395,6 +8252,9 @@
       <c r="F290" t="n">
         <v>32600</v>
       </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -7419,6 +8279,9 @@
       <c r="F291" t="n">
         <v>18667</v>
       </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -7443,6 +8306,9 @@
       <c r="F292" t="n">
         <v>70600</v>
       </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -7467,6 +8333,9 @@
       <c r="F293" t="n">
         <v>50600</v>
       </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -7491,6 +8360,9 @@
       <c r="F294" t="n">
         <v>29280</v>
       </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -7515,6 +8387,9 @@
       <c r="F295" t="n">
         <v>50050</v>
       </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7533,11 +8408,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F296" t="n">
         <v>39040</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -7563,6 +8441,9 @@
       <c r="F297" t="n">
         <v>50050</v>
       </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -7587,6 +8468,9 @@
       <c r="F298" t="n">
         <v>50050</v>
       </c>
+      <c r="G298" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -7611,6 +8495,9 @@
       <c r="F299" t="n">
         <v>14400</v>
       </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -7629,11 +8516,14 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F300" t="n">
         <v>39040</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -7653,11 +8543,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F301" t="n">
         <v>39040</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7683,6 +8576,9 @@
       <c r="F302" t="n">
         <v>70600</v>
       </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -7707,6 +8603,9 @@
       <c r="F303" t="n">
         <v>50600</v>
       </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -7731,6 +8630,9 @@
       <c r="F304" t="n">
         <v>60600</v>
       </c>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -7755,6 +8657,9 @@
       <c r="F305" t="n">
         <v>60600</v>
       </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -7779,6 +8684,9 @@
       <c r="F306" t="n">
         <v>40600</v>
       </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -7803,6 +8711,9 @@
       <c r="F307" t="n">
         <v>32600</v>
       </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -7827,6 +8738,9 @@
       <c r="F308" t="n">
         <v>182700</v>
       </c>
+      <c r="G308" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -7851,6 +8765,9 @@
       <c r="F309" t="n">
         <v>30600</v>
       </c>
+      <c r="G309" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -7875,6 +8792,9 @@
       <c r="F310" t="n">
         <v>135900</v>
       </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -7899,6 +8819,9 @@
       <c r="F311" t="n">
         <v>70600</v>
       </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -7923,6 +8846,9 @@
       <c r="F312" t="n">
         <v>41220</v>
       </c>
+      <c r="G312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7947,6 +8873,9 @@
       <c r="F313" t="n">
         <v>45300</v>
       </c>
+      <c r="G313" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7971,6 +8900,9 @@
       <c r="F314" t="n">
         <v>41220</v>
       </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7989,11 +8921,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F315" t="n">
         <v>23900</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8019,6 +8954,9 @@
       <c r="F316" t="n">
         <v>65556</v>
       </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -8043,6 +8981,9 @@
       <c r="F317" t="n">
         <v>24400</v>
       </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -8067,6 +9008,9 @@
       <c r="F318" t="n">
         <v>29280</v>
       </c>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -8091,6 +9035,9 @@
       <c r="F319" t="n">
         <v>24400</v>
       </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -8115,6 +9062,9 @@
       <c r="F320" t="n">
         <v>36640</v>
       </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -8139,6 +9089,9 @@
       <c r="F321" t="n">
         <v>18977</v>
       </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -8163,6 +9116,9 @@
       <c r="F322" t="n">
         <v>19520</v>
       </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -8187,6 +9143,9 @@
       <c r="F323" t="n">
         <v>32600</v>
       </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -8211,6 +9170,9 @@
       <c r="F324" t="n">
         <v>46300</v>
       </c>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -8235,6 +9197,9 @@
       <c r="F325" t="n">
         <v>32600</v>
       </c>
+      <c r="G325" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -8259,6 +9224,9 @@
       <c r="F326" t="n">
         <v>32600</v>
       </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -8283,6 +9251,9 @@
       <c r="F327" t="n">
         <v>17900</v>
       </c>
+      <c r="G327" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -8307,6 +9278,9 @@
       <c r="F328" t="n">
         <v>15800</v>
       </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -8331,6 +9305,9 @@
       <c r="F329" t="n">
         <v>44600</v>
       </c>
+      <c r="G329" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -8355,6 +9332,9 @@
       <c r="F330" t="n">
         <v>32600</v>
       </c>
+      <c r="G330" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -8379,6 +9359,9 @@
       <c r="F331" t="n">
         <v>13940</v>
       </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -8403,6 +9386,9 @@
       <c r="F332" t="n">
         <v>34600</v>
       </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -8427,6 +9413,9 @@
       <c r="F333" t="n">
         <v>39800</v>
       </c>
+      <c r="G333" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -8451,6 +9440,9 @@
       <c r="F334" t="n">
         <v>39800</v>
       </c>
+      <c r="G334" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -8475,6 +9467,9 @@
       <c r="F335" t="n">
         <v>42400</v>
       </c>
+      <c r="G335" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -8493,11 +9488,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F336" t="n">
         <v>24400</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -8523,6 +9521,9 @@
       <c r="F337" t="n">
         <v>48800</v>
       </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -8547,6 +9548,9 @@
       <c r="F338" t="n">
         <v>24400</v>
       </c>
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -8571,6 +9575,9 @@
       <c r="F339" t="n">
         <v>38500</v>
       </c>
+      <c r="G339" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -8595,6 +9602,9 @@
       <c r="F340" t="n">
         <v>76180</v>
       </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -8619,6 +9629,9 @@
       <c r="F341" t="n">
         <v>46300</v>
       </c>
+      <c r="G341" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -8643,6 +9656,9 @@
       <c r="F342" t="n">
         <v>55856</v>
       </c>
+      <c r="G342" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -8667,6 +9683,9 @@
       <c r="F343" t="n">
         <v>42400</v>
       </c>
+      <c r="G343" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -8691,6 +9710,9 @@
       <c r="F344" t="n">
         <v>42600</v>
       </c>
+      <c r="G344" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -8715,6 +9737,9 @@
       <c r="F345" t="n">
         <v>39800</v>
       </c>
+      <c r="G345" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -8739,6 +9764,9 @@
       <c r="F346" t="n">
         <v>35518</v>
       </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -8763,6 +9791,9 @@
       <c r="F347" t="n">
         <v>44600</v>
       </c>
+      <c r="G347" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -8787,6 +9818,9 @@
       <c r="F348" t="n">
         <v>43700</v>
       </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -8811,6 +9845,9 @@
       <c r="F349" t="n">
         <v>32600</v>
       </c>
+      <c r="G349" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -8835,6 +9872,9 @@
       <c r="F350" t="n">
         <v>138900</v>
       </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -8859,6 +9899,9 @@
       <c r="F351" t="n">
         <v>39800</v>
       </c>
+      <c r="G351" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -8883,6 +9926,9 @@
       <c r="F352" t="n">
         <v>138900</v>
       </c>
+      <c r="G352" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -8907,6 +9953,9 @@
       <c r="F353" t="n">
         <v>32600</v>
       </c>
+      <c r="G353" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -8931,6 +9980,9 @@
       <c r="F354" t="n">
         <v>37144</v>
       </c>
+      <c r="G354" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -8949,11 +10001,14 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F355" t="n">
         <v>500</v>
+      </c>
+      <c r="G355" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -8979,6 +10034,9 @@
       <c r="F356" t="n">
         <v>23900</v>
       </c>
+      <c r="G356" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -9003,6 +10061,9 @@
       <c r="F357" t="n">
         <v>46300</v>
       </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -9027,6 +10088,9 @@
       <c r="F358" t="n">
         <v>43020</v>
       </c>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -9045,11 +10109,14 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Economics 4+1</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F359" t="n">
         <v>23900</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -9075,6 +10142,9 @@
       <c r="F360" t="n">
         <v>62651</v>
       </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -9099,6 +10169,9 @@
       <c r="F361" t="n">
         <v>22059.6</v>
       </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -9123,6 +10196,9 @@
       <c r="F362" t="n">
         <v>58250</v>
       </c>
+      <c r="G362" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -9147,6 +10223,9 @@
       <c r="F363" t="n">
         <v>34850</v>
       </c>
+      <c r="G363" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -9171,6 +10250,9 @@
       <c r="F364" t="n">
         <v>54960</v>
       </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -9195,6 +10277,9 @@
       <c r="F365" t="n">
         <v>38006</v>
       </c>
+      <c r="G365" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -9219,6 +10304,9 @@
       <c r="F366" t="n">
         <v>38006</v>
       </c>
+      <c r="G366" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -9243,6 +10331,9 @@
       <c r="F367" t="n">
         <v>37950</v>
       </c>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -9267,6 +10358,9 @@
       <c r="F368" t="n">
         <v>15900</v>
       </c>
+      <c r="G368" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -9291,6 +10385,9 @@
       <c r="F369" t="n">
         <v>64600</v>
       </c>
+      <c r="G369" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -9315,6 +10412,9 @@
       <c r="F370" t="n">
         <v>41992</v>
       </c>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -9339,6 +10439,9 @@
       <c r="F371" t="n">
         <v>39334</v>
       </c>
+      <c r="G371" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -9363,6 +10466,9 @@
       <c r="F372" t="n">
         <v>14640</v>
       </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -9387,6 +10493,9 @@
       <c r="F373" t="n">
         <v>39334</v>
       </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -9411,6 +10520,9 @@
       <c r="F374" t="n">
         <v>39334</v>
       </c>
+      <c r="G374" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -9435,6 +10547,9 @@
       <c r="F375" t="n">
         <v>44600</v>
       </c>
+      <c r="G375" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -9459,6 +10574,9 @@
       <c r="F376" t="n">
         <v>22800</v>
       </c>
+      <c r="G376" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -9483,6 +10601,9 @@
       <c r="F377" t="n">
         <v>74600</v>
       </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -9507,6 +10628,9 @@
       <c r="F378" t="n">
         <v>41990</v>
       </c>
+      <c r="G378" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -9531,6 +10655,9 @@
       <c r="F379" t="n">
         <v>57200</v>
       </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -9555,6 +10682,9 @@
       <c r="F380" t="n">
         <v>94600</v>
       </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -9579,6 +10709,9 @@
       <c r="F381" t="n">
         <v>48800</v>
       </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -9603,6 +10736,9 @@
       <c r="F382" t="n">
         <v>39666</v>
       </c>
+      <c r="G382" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -9627,6 +10763,9 @@
       <c r="F383" t="n">
         <v>27550</v>
       </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -9651,6 +10790,9 @@
       <c r="F384" t="n">
         <v>41934</v>
       </c>
+      <c r="G384" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -9675,6 +10817,9 @@
       <c r="F385" t="n">
         <v>23400</v>
       </c>
+      <c r="G385" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -9699,6 +10844,9 @@
       <c r="F386" t="n">
         <v>23400</v>
       </c>
+      <c r="G386" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -9723,6 +10871,9 @@
       <c r="F387" t="n">
         <v>11700</v>
       </c>
+      <c r="G387" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -9747,6 +10898,9 @@
       <c r="F388" t="n">
         <v>43318</v>
       </c>
+      <c r="G388" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -9771,6 +10925,9 @@
       <c r="F389" t="n">
         <v>57200</v>
       </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -9795,6 +10952,9 @@
       <c r="F390" t="n">
         <v>47302</v>
       </c>
+      <c r="G390" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -9819,6 +10979,9 @@
       <c r="F391" t="n">
         <v>64066</v>
       </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -9843,6 +11006,9 @@
       <c r="F392" t="n">
         <v>45360</v>
       </c>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -9867,6 +11033,9 @@
       <c r="F393" t="n">
         <v>39334</v>
       </c>
+      <c r="G393" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -9891,6 +11060,9 @@
       <c r="F394" t="n">
         <v>44646</v>
       </c>
+      <c r="G394" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -9915,6 +11087,9 @@
       <c r="F395" t="n">
         <v>44646</v>
       </c>
+      <c r="G395" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -9939,6 +11114,9 @@
       <c r="F396" t="n">
         <v>35350</v>
       </c>
+      <c r="G396" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -9963,6 +11141,9 @@
       <c r="F397" t="n">
         <v>39334</v>
       </c>
+      <c r="G397" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -9987,6 +11168,9 @@
       <c r="F398" t="n">
         <v>38006</v>
       </c>
+      <c r="G398" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -10011,6 +11195,9 @@
       <c r="F399" t="n">
         <v>47300</v>
       </c>
+      <c r="G399" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -10035,6 +11222,9 @@
       <c r="F400" t="n">
         <v>40636</v>
       </c>
+      <c r="G400" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -10059,6 +11249,9 @@
       <c r="F401" t="n">
         <v>39334</v>
       </c>
+      <c r="G401" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -10083,6 +11276,9 @@
       <c r="F402" t="n">
         <v>64600</v>
       </c>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -10107,6 +11303,9 @@
       <c r="F403" t="n">
         <v>78474</v>
       </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -10131,6 +11330,9 @@
       <c r="F404" t="n">
         <v>48800</v>
       </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -10155,6 +11357,9 @@
       <c r="F405" t="n">
         <v>72155</v>
       </c>
+      <c r="G405" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -10179,6 +11384,9 @@
       <c r="F406" t="n">
         <v>36600</v>
       </c>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -10203,6 +11411,9 @@
       <c r="F407" t="n">
         <v>36600</v>
       </c>
+      <c r="G407" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -10227,6 +11438,9 @@
       <c r="F408" t="n">
         <v>40166</v>
       </c>
+      <c r="G408" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -10251,6 +11465,9 @@
       <c r="F409" t="n">
         <v>48300</v>
       </c>
+      <c r="G409" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -10275,6 +11492,9 @@
       <c r="F410" t="n">
         <v>40166</v>
       </c>
+      <c r="G410" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -10299,6 +11519,9 @@
       <c r="F411" t="n">
         <v>42877</v>
       </c>
+      <c r="G411" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -10323,6 +11546,9 @@
       <c r="F412" t="n">
         <v>40166</v>
       </c>
+      <c r="G412" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -10347,6 +11573,9 @@
       <c r="F413" t="n">
         <v>38811</v>
       </c>
+      <c r="G413" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -10371,6 +11600,9 @@
       <c r="F414" t="n">
         <v>38800</v>
       </c>
+      <c r="G414" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -10395,6 +11627,9 @@
       <c r="F415" t="n">
         <v>56600</v>
       </c>
+      <c r="G415" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -10419,6 +11654,9 @@
       <c r="F416" t="n">
         <v>58424</v>
       </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -10443,6 +11681,9 @@
       <c r="F417" t="n">
         <v>24400</v>
       </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -10467,6 +11708,9 @@
       <c r="F418" t="n">
         <v>40166</v>
       </c>
+      <c r="G418" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -10491,6 +11735,9 @@
       <c r="F419" t="n">
         <v>25228</v>
       </c>
+      <c r="G419" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -10515,6 +11762,9 @@
       <c r="F420" t="n">
         <v>40166</v>
       </c>
+      <c r="G420" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -10539,6 +11789,9 @@
       <c r="F421" t="n">
         <v>40166</v>
       </c>
+      <c r="G421" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -10563,6 +11816,9 @@
       <c r="F422" t="n">
         <v>56600</v>
       </c>
+      <c r="G422" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -10587,6 +11843,9 @@
       <c r="F423" t="n">
         <v>36100</v>
       </c>
+      <c r="G423" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -10611,6 +11870,9 @@
       <c r="F424" t="n">
         <v>38811</v>
       </c>
+      <c r="G424" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -10635,6 +11897,9 @@
       <c r="F425" t="n">
         <v>44233</v>
       </c>
+      <c r="G425" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -10659,6 +11924,9 @@
       <c r="F426" t="n">
         <v>58424</v>
       </c>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -10683,6 +11951,9 @@
       <c r="F427" t="n">
         <v>24400</v>
       </c>
+      <c r="G427" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -10707,6 +11978,9 @@
       <c r="F428" t="n">
         <v>56600</v>
       </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -10731,6 +12005,9 @@
       <c r="F429" t="n">
         <v>18800</v>
       </c>
+      <c r="G429" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -10755,6 +12032,9 @@
       <c r="F430" t="n">
         <v>36350</v>
       </c>
+      <c r="G430" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -10779,6 +12059,9 @@
       <c r="F431" t="n">
         <v>36100</v>
       </c>
+      <c r="G431" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -10803,6 +12086,9 @@
       <c r="F432" t="n">
         <v>26600</v>
       </c>
+      <c r="G432" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -10827,6 +12113,9 @@
       <c r="F433" t="n">
         <v>37428</v>
       </c>
+      <c r="G433" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -10851,6 +12140,9 @@
       <c r="F434" t="n">
         <v>58424</v>
       </c>
+      <c r="G434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -10875,6 +12167,9 @@
       <c r="F435" t="n">
         <v>37455</v>
       </c>
+      <c r="G435" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -10899,6 +12194,9 @@
       <c r="F436" t="n">
         <v>38811</v>
       </c>
+      <c r="G436" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -10923,6 +12221,9 @@
       <c r="F437" t="n">
         <v>45588</v>
       </c>
+      <c r="G437" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -10947,6 +12248,9 @@
       <c r="F438" t="n">
         <v>40167</v>
       </c>
+      <c r="G438" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -10971,6 +12275,9 @@
       <c r="F439" t="n">
         <v>33361</v>
       </c>
+      <c r="G439" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -10995,6 +12302,9 @@
       <c r="F440" t="n">
         <v>36100</v>
       </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -11019,6 +12329,9 @@
       <c r="F441" t="n">
         <v>40166</v>
       </c>
+      <c r="G441" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -11043,6 +12356,9 @@
       <c r="F442" t="n">
         <v>36100</v>
       </c>
+      <c r="G442" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -11067,6 +12383,9 @@
       <c r="F443" t="n">
         <v>40166</v>
       </c>
+      <c r="G443" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -11091,6 +12410,9 @@
       <c r="F444" t="n">
         <v>23900</v>
       </c>
+      <c r="G444" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -11115,6 +12437,9 @@
       <c r="F445" t="n">
         <v>40166</v>
       </c>
+      <c r="G445" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -11139,6 +12464,9 @@
       <c r="F446" t="n">
         <v>40166</v>
       </c>
+      <c r="G446" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -11163,6 +12491,9 @@
       <c r="F447" t="n">
         <v>40166</v>
       </c>
+      <c r="G447" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -11187,6 +12518,9 @@
       <c r="F448" t="n">
         <v>58424</v>
       </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -11211,6 +12545,9 @@
       <c r="F449" t="n">
         <v>58424</v>
       </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -11235,6 +12572,9 @@
       <c r="F450" t="n">
         <v>36741</v>
       </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -11259,6 +12599,9 @@
       <c r="F451" t="n">
         <v>48800</v>
       </c>
+      <c r="G451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -11283,6 +12626,9 @@
       <c r="F452" t="n">
         <v>58424</v>
       </c>
+      <c r="G452" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -11307,6 +12653,9 @@
       <c r="F453" t="n">
         <v>27800</v>
       </c>
+      <c r="G453" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -11331,6 +12680,9 @@
       <c r="F454" t="n">
         <v>33800</v>
       </c>
+      <c r="G454" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -11355,6 +12707,9 @@
       <c r="F455" t="n">
         <v>39040</v>
       </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -11379,6 +12734,9 @@
       <c r="F456" t="n">
         <v>40666</v>
       </c>
+      <c r="G456" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -11403,6 +12761,9 @@
       <c r="F457" t="n">
         <v>23800</v>
       </c>
+      <c r="G457" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -11427,6 +12788,9 @@
       <c r="F458" t="n">
         <v>29280</v>
       </c>
+      <c r="G458" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -11451,6 +12815,9 @@
       <c r="F459" t="n">
         <v>48800</v>
       </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -11475,6 +12842,9 @@
       <c r="F460" t="n">
         <v>48800</v>
       </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -11499,6 +12869,9 @@
       <c r="F461" t="n">
         <v>36600</v>
       </c>
+      <c r="G461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -11523,6 +12896,9 @@
       <c r="F462" t="n">
         <v>14640</v>
       </c>
+      <c r="G462" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -11547,6 +12923,9 @@
       <c r="F463" t="n">
         <v>48800</v>
       </c>
+      <c r="G463" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -11571,6 +12950,9 @@
       <c r="F464" t="n">
         <v>29280</v>
       </c>
+      <c r="G464" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -11595,6 +12977,9 @@
       <c r="F465" t="n">
         <v>14640</v>
       </c>
+      <c r="G465" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -11619,6 +13004,9 @@
       <c r="F466" t="n">
         <v>13800</v>
       </c>
+      <c r="G466" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -11643,6 +13031,9 @@
       <c r="F467" t="n">
         <v>13800</v>
       </c>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -11667,6 +13058,9 @@
       <c r="F468" t="n">
         <v>14640</v>
       </c>
+      <c r="G468" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -11691,6 +13085,9 @@
       <c r="F469" t="n">
         <v>23800</v>
       </c>
+      <c r="G469" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -11715,6 +13112,9 @@
       <c r="F470" t="n">
         <v>18800</v>
       </c>
+      <c r="G470" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -11739,6 +13139,9 @@
       <c r="F471" t="n">
         <v>43800</v>
       </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -11763,6 +13166,9 @@
       <c r="F472" t="n">
         <v>23800</v>
       </c>
+      <c r="G472" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -11787,6 +13193,9 @@
       <c r="F473" t="n">
         <v>29280</v>
       </c>
+      <c r="G473" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -11811,6 +13220,9 @@
       <c r="F474" t="n">
         <v>29280</v>
       </c>
+      <c r="G474" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -11835,6 +13247,9 @@
       <c r="F475" t="n">
         <v>48800</v>
       </c>
+      <c r="G475" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -11859,6 +13274,9 @@
       <c r="F476" t="n">
         <v>48800</v>
       </c>
+      <c r="G476" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -11883,6 +13301,9 @@
       <c r="F477" t="n">
         <v>48800</v>
       </c>
+      <c r="G477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -11907,6 +13328,9 @@
       <c r="F478" t="n">
         <v>29280</v>
       </c>
+      <c r="G478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -11931,6 +13355,9 @@
       <c r="F479" t="n">
         <v>29280</v>
       </c>
+      <c r="G479" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -11955,6 +13382,9 @@
       <c r="F480" t="n">
         <v>29280</v>
       </c>
+      <c r="G480" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -11979,6 +13409,9 @@
       <c r="F481" t="n">
         <v>14640</v>
       </c>
+      <c r="G481" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -12003,6 +13436,9 @@
       <c r="F482" t="n">
         <v>48800</v>
       </c>
+      <c r="G482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -12027,6 +13463,9 @@
       <c r="F483" t="n">
         <v>29280</v>
       </c>
+      <c r="G483" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -12051,6 +13490,9 @@
       <c r="F484" t="n">
         <v>23800</v>
       </c>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -12075,6 +13517,9 @@
       <c r="F485" t="n">
         <v>48800</v>
       </c>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -12099,6 +13544,9 @@
       <c r="F486" t="n">
         <v>43920</v>
       </c>
+      <c r="G486" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -12123,6 +13571,9 @@
       <c r="F487" t="n">
         <v>43377</v>
       </c>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -12147,6 +13598,9 @@
       <c r="F488" t="n">
         <v>14640</v>
       </c>
+      <c r="G488" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -12171,6 +13625,9 @@
       <c r="F489" t="n">
         <v>14640</v>
       </c>
+      <c r="G489" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -12195,6 +13652,9 @@
       <c r="F490" t="n">
         <v>14640</v>
       </c>
+      <c r="G490" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -12219,6 +13679,9 @@
       <c r="F491" t="n">
         <v>9760</v>
       </c>
+      <c r="G491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -12243,6 +13706,9 @@
       <c r="F492" t="n">
         <v>14640</v>
       </c>
+      <c r="G492" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -12267,6 +13733,9 @@
       <c r="F493" t="n">
         <v>14640</v>
       </c>
+      <c r="G493" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -12290,6 +13759,9 @@
       </c>
       <c r="F494" t="n">
         <v>14640</v>
+      </c>
+      <c r="G494" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
